--- a/AAII_Financials/Quarterly/JSAIY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/JSAIY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="349" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="391" uniqueCount="92">
   <si>
     <t>JSAIY</t>
   </si>
@@ -656,28 +656,28 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AE102"/>
+  <dimension ref="A5:AG102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="25" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="27" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
@@ -685,49 +685,51 @@
     <col min="29" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="31" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="16384" width="9.140625" style="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46081</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45991</v>
+      </c>
+      <c r="F7" s="2">
         <v>45913</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45821</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45717</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45627</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45549</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45457</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45353</v>
-      </c>
-      <c r="K7" s="2">
-        <v>45262</v>
-      </c>
-      <c r="L7" s="2">
-        <v>45185</v>
       </c>
       <c r="M7" s="2">
         <v>45262</v>
@@ -736,58 +738,64 @@
         <v>45185</v>
       </c>
       <c r="O7" s="2">
+        <v>45262</v>
+      </c>
+      <c r="P7" s="2">
+        <v>45185</v>
+      </c>
+      <c r="Q7" s="2">
         <v>44821</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44625</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44457</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44261</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>44093</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43897</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43729</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43533</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43365</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>43169</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43001</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>42805</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>42637</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>42441</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>42273</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>42077</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>41909</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -824,59 +832,65 @@
       <c r="N8" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O8" s="3">
+      <c r="O8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q8" s="3">
         <v>21530600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>18595200</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>20633000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>18520400</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>19042300</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>17610400</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>18732400</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>16418700</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>18453400</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>18836700</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>20722900</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>17939000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>16343700</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AD8" s="3">
         <v>14460900</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AE8" s="3">
         <v>16198200</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AF8" s="3">
         <v>14626900</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AG8" s="3">
         <v>16679800</v>
       </c>
     </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -913,59 +927,65 @@
       <c r="N9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O9" s="3">
+      <c r="O9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q9" s="3">
         <v>19923100</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>17140000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>18995400</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>17355200</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>17397500</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>16130200</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>17335200</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>15099700</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Y9" s="3">
         <v>17022500</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Z9" s="3">
         <v>17614700</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="AA9" s="3">
         <v>19327600</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AB9" s="3">
         <v>16791200</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AC9" s="3">
         <v>15354700</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AD9" s="3">
         <v>13549200</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AE9" s="3">
         <v>15210900</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AF9" s="3">
         <v>13693300</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AG9" s="3">
         <v>16022700</v>
       </c>
     </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
@@ -1002,59 +1022,65 @@
       <c r="N10" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O10" s="3">
+      <c r="O10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q10" s="3">
         <v>1607400</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>1455200</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>1637600</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>1165200</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>1644900</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>1480200</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>1397100</v>
       </c>
-      <c r="V10" s="3">
+      <c r="X10" s="3">
         <v>1318900</v>
       </c>
-      <c r="W10" s="3">
+      <c r="Y10" s="3">
         <v>1430900</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Z10" s="3">
         <v>1222000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="AA10" s="3">
         <v>1395300</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AB10" s="3">
         <v>1147800</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AC10" s="3">
         <v>989000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AD10" s="3">
         <v>911700</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AE10" s="3">
         <v>987400</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AF10" s="3">
         <v>933600</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AG10" s="3">
         <v>657100</v>
       </c>
     </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1086,8 +1112,10 @@
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
-    </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF11" s="3"/>
+      <c r="AG11" s="3"/>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1175,8 +1203,14 @@
       <c r="AE12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1264,8 +1298,14 @@
       <c r="AE13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1302,50 +1342,50 @@
       <c r="N14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O14" s="3">
+      <c r="O14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q14" s="3">
         <v>-7900</v>
       </c>
-      <c r="P14" s="3">
+      <c r="R14" s="3">
         <v>28900</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="S14" s="3">
         <v>-147000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="T14" s="3">
         <v>112800</v>
       </c>
-      <c r="S14" s="3">
+      <c r="U14" s="3">
         <v>555900</v>
       </c>
-      <c r="T14" s="3">
+      <c r="V14" s="3">
         <v>140700</v>
       </c>
-      <c r="U14" s="3">
+      <c r="W14" s="3">
         <v>277900</v>
       </c>
-      <c r="V14" s="3">
+      <c r="X14" s="3">
         <v>30800</v>
       </c>
-      <c r="W14" s="3">
+      <c r="Y14" s="3">
         <v>-17100</v>
       </c>
-      <c r="X14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Y14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Z14" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AA14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC14" s="3">
-        <v>0</v>
+      <c r="AB14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AD14" s="3">
         <v>0</v>
@@ -1353,8 +1393,14 @@
       <c r="AE14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1391,11 +1437,11 @@
       <c r="N15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O15" s="3">
-        <v>0</v>
-      </c>
-      <c r="P15" s="3">
-        <v>0</v>
+      <c r="O15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P15" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q15" s="3">
         <v>0</v>
@@ -1442,8 +1488,14 @@
       <c r="AE15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1472,8 +1524,10 @@
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
-    </row>
-    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF16" s="3"/>
+      <c r="AG16" s="3"/>
+    </row>
+    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1510,59 +1564,65 @@
       <c r="N17" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O17" s="3">
+      <c r="O17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q17" s="3">
         <v>20832500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>17969300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>19753900</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>18368200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>18967100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>17069300</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>18419700</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>16096900</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>18063100</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>18516200</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>20322400</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>17694600</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>15752900</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>14090500</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>15646500</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AF17" s="3">
         <v>14212100</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AG17" s="3">
         <v>16987900</v>
       </c>
     </row>
-    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1599,59 +1659,65 @@
       <c r="N18" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O18" s="3">
+      <c r="O18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q18" s="3">
         <v>698100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>625900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>879200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>152200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>75200</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>541100</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>312700</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>321700</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>390400</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>320500</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>400500</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>244300</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>590800</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>370400</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AE18" s="3">
         <v>551700</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AF18" s="3">
         <v>414800</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AG18" s="3">
         <v>-308100</v>
       </c>
     </row>
-    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1683,8 +1749,10 @@
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
-    </row>
-    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF19" s="3"/>
+      <c r="AG19" s="3"/>
+    </row>
+    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1721,59 +1789,65 @@
       <c r="N20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O20" s="3">
+      <c r="O20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q20" s="3">
         <v>6600</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>-31500</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>36700</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>10500</v>
       </c>
-      <c r="S20" s="3">
+      <c r="U20" s="3">
         <v>-6400</v>
       </c>
-      <c r="T20" s="3">
+      <c r="V20" s="3">
         <v>-10100</v>
       </c>
-      <c r="U20" s="3">
+      <c r="W20" s="3">
         <v>-43400</v>
       </c>
-      <c r="V20" s="3">
+      <c r="X20" s="3">
         <v>10600</v>
       </c>
-      <c r="W20" s="3">
+      <c r="Y20" s="3">
         <v>11000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Z20" s="3">
         <v>8200</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="AA20" s="3">
         <v>-8500</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AB20" s="3">
         <v>-2600</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AC20" s="3">
         <v>-29700</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AD20" s="3">
         <v>-24800</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AE20" s="3">
         <v>-26100</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AF20" s="3">
         <v>-48700</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AG20" s="3">
         <v>9200</v>
       </c>
     </row>
-    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1810,59 +1884,65 @@
       <c r="N21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O21" s="3">
+      <c r="O21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q21" s="3">
         <v>1557600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>1330600</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>1780700</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>934300</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>911700</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>1277400</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>1096900</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>1019700</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>1232100</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>831900</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>904300</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AB21" s="3">
         <v>639300</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AC21" s="3">
         <v>983800</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AD21" s="3">
         <v>705600</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AE21" s="3">
         <v>927400</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AF21" s="3">
         <v>709700</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AG21" s="3">
         <v>119800</v>
       </c>
     </row>
-    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1899,59 +1979,65 @@
       <c r="N22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O22" s="3">
+      <c r="O22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q22" s="3">
         <v>211300</v>
       </c>
-      <c r="P22" s="3">
+      <c r="R22" s="3">
         <v>183700</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="S22" s="3">
         <v>224400</v>
       </c>
-      <c r="R22" s="3">
+      <c r="T22" s="3">
         <v>196800</v>
       </c>
-      <c r="S22" s="3">
+      <c r="U22" s="3">
         <v>243500</v>
       </c>
-      <c r="T22" s="3">
+      <c r="V22" s="3">
         <v>219200</v>
       </c>
-      <c r="U22" s="3">
+      <c r="W22" s="3">
         <v>258100</v>
       </c>
-      <c r="V22" s="3">
+      <c r="X22" s="3">
         <v>220000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="Y22" s="3">
         <v>270800</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Z22" s="3">
         <v>70900</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="AA22" s="3">
         <v>80700</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AB22" s="3">
         <v>68700</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AC22" s="3">
         <v>80200</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AD22" s="3">
         <v>73000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AE22" s="3">
         <v>83500</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AF22" s="3">
         <v>79000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AG22" s="3">
         <v>83000</v>
       </c>
     </row>
-    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1988,59 +2074,65 @@
       <c r="N23" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O23" s="3">
+      <c r="O23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q23" s="3">
         <v>493400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>410700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>691500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>-34100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>-174700</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>311800</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>11200</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>112400</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>130500</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>257800</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>311300</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>173000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>480900</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>272600</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>442200</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AF23" s="3">
         <v>287100</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AG23" s="3">
         <v>-381900</v>
       </c>
     </row>
-    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2077,59 +2169,65 @@
       <c r="N24" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O24" s="3">
+      <c r="O24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q24" s="3">
         <v>119400</v>
       </c>
-      <c r="P24" s="3">
+      <c r="R24" s="3">
         <v>32800</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="S24" s="3">
         <v>195500</v>
       </c>
-      <c r="R24" s="3">
+      <c r="T24" s="3">
         <v>-6600</v>
       </c>
-      <c r="S24" s="3">
+      <c r="U24" s="3">
         <v>53600</v>
       </c>
-      <c r="T24" s="3">
+      <c r="V24" s="3">
         <v>71000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="W24" s="3">
         <v>58300</v>
       </c>
-      <c r="V24" s="3">
+      <c r="X24" s="3">
         <v>37900</v>
       </c>
-      <c r="W24" s="3">
+      <c r="Y24" s="3">
         <v>-19500</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Z24" s="3">
         <v>62700</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="AA24" s="3">
         <v>76400</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AB24" s="3">
         <v>70000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AC24" s="3">
         <v>94400</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AD24" s="3">
         <v>2600</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AE24" s="3">
         <v>97800</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AF24" s="3">
         <v>52700</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AG24" s="3">
         <v>71100</v>
       </c>
     </row>
-    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2217,8 +2315,14 @@
       <c r="AE25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -2255,59 +2359,65 @@
       <c r="N26" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O26" s="3">
+      <c r="O26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q26" s="3">
         <v>374000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>377900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>496000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>-27600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>-228200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>240800</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>-47200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>74500</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>150000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>195000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>234900</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>103000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>386600</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>270000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AE26" s="3">
         <v>344300</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AF26" s="3">
         <v>234400</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AG26" s="3">
         <v>-453000</v>
       </c>
     </row>
-    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -2344,59 +2454,65 @@
       <c r="N27" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O27" s="3">
+      <c r="O27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q27" s="3">
         <v>374000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>377900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>496000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>-31500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>-233300</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>225600</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>-60800</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>65100</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>137800</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>184100</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>220800</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>92500</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>373600</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>256900</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AE27" s="3">
         <v>341700</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AF27" s="3">
         <v>234400</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AG27" s="3">
         <v>-453000</v>
       </c>
     </row>
-    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2484,8 +2600,14 @@
       <c r="AE28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2522,11 +2644,11 @@
       <c r="N29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O29" s="3">
-        <v>0</v>
-      </c>
-      <c r="P29" s="3">
-        <v>0</v>
+      <c r="O29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q29" s="3">
         <v>0</v>
@@ -2573,8 +2695,14 @@
       <c r="AE29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2662,8 +2790,14 @@
       <c r="AE30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2751,8 +2885,14 @@
       <c r="AE31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2789,59 +2929,65 @@
       <c r="N32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O32" s="3">
+      <c r="O32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q32" s="3">
         <v>-6600</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>31500</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>-36700</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>-10500</v>
       </c>
-      <c r="S32" s="3">
+      <c r="U32" s="3">
         <v>6400</v>
       </c>
-      <c r="T32" s="3">
+      <c r="V32" s="3">
         <v>10100</v>
       </c>
-      <c r="U32" s="3">
+      <c r="W32" s="3">
         <v>43400</v>
       </c>
-      <c r="V32" s="3">
+      <c r="X32" s="3">
         <v>-10600</v>
       </c>
-      <c r="W32" s="3">
+      <c r="Y32" s="3">
         <v>-11000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Z32" s="3">
         <v>-8200</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="AA32" s="3">
         <v>8500</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AB32" s="3">
         <v>2600</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AC32" s="3">
         <v>29700</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AD32" s="3">
         <v>24800</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AE32" s="3">
         <v>26100</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AF32" s="3">
         <v>48700</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AG32" s="3">
         <v>-9200</v>
       </c>
     </row>
-    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -2878,59 +3024,65 @@
       <c r="N33" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O33" s="3">
+      <c r="O33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q33" s="3">
         <v>374000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>377900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>496000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>-31500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>-233300</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>225600</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>-60800</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>65100</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>137800</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>184100</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>220800</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>92500</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>373600</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>256900</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3">
         <v>341700</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AF33" s="3">
         <v>234400</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AG33" s="3">
         <v>-453000</v>
       </c>
     </row>
-    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3018,8 +3170,14 @@
       <c r="AE34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -3056,93 +3214,99 @@
       <c r="N35" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O35" s="3">
+      <c r="O35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q35" s="3">
         <v>374000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>377900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>496000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>-31500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>-233300</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>225600</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>-60800</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>65100</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>137800</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>184100</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>220800</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>92500</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>373600</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>256900</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3">
         <v>341700</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AF35" s="3">
         <v>234400</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AG35" s="3">
         <v>-453000</v>
       </c>
     </row>
-    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46081</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45991</v>
+      </c>
+      <c r="F38" s="2">
         <v>45913</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45821</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45717</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45627</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45549</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45457</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45353</v>
-      </c>
-      <c r="K38" s="2">
-        <v>45262</v>
-      </c>
-      <c r="L38" s="2">
-        <v>45185</v>
       </c>
       <c r="M38" s="2">
         <v>45262</v>
@@ -3151,58 +3315,64 @@
         <v>45185</v>
       </c>
       <c r="O38" s="2">
+        <v>45262</v>
+      </c>
+      <c r="P38" s="2">
+        <v>45185</v>
+      </c>
+      <c r="Q38" s="2">
         <v>44821</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44625</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44457</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44261</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>44093</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43897</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43729</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43533</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43365</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>43169</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43001</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>42805</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>42637</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>42441</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>42273</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>42077</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>41909</v>
       </c>
     </row>
-    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3234,8 +3404,10 @@
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
-    </row>
-    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF39" s="3"/>
+      <c r="AG39" s="3"/>
+    </row>
+    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3267,37 +3439,39 @@
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
-    </row>
-    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF40" s="3"/>
+      <c r="AG40" s="3"/>
+    </row>
+    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>981100</v>
+      </c>
+      <c r="E41" s="3">
+        <v>965000</v>
+      </c>
+      <c r="F41" s="3">
         <v>1199300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>1203100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>914900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>923600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>1194800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>1152800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>1108100</v>
-      </c>
-      <c r="K41" s="3">
-        <v>2518500</v>
-      </c>
-      <c r="L41" s="3">
-        <v>1076500</v>
       </c>
       <c r="M41" s="3">
         <v>2518500</v>
@@ -3306,73 +3480,79 @@
         <v>1076500</v>
       </c>
       <c r="O41" s="3">
+        <v>2518500</v>
+      </c>
+      <c r="P41" s="3">
+        <v>1076500</v>
+      </c>
+      <c r="Q41" s="3">
         <v>1558900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>775500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>1426400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>948700</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>2111600</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>2173400</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>1372300</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>961700</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>1095500</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>1427900</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>1542500</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>1112100</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>1383300</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AD41" s="3">
         <v>1113900</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AE41" s="3">
         <v>1494700</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AF41" s="3">
         <v>1692100</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AG41" s="3">
         <v>1865900</v>
       </c>
     </row>
-    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>0</v>
+      </c>
+      <c r="E42" s="3">
+        <v>0</v>
+      </c>
+      <c r="F42" s="3">
         <v>16300</v>
       </c>
-      <c r="E42" s="3">
+      <c r="G42" s="3">
         <v>16300</v>
       </c>
-      <c r="F42" s="3">
-        <v>0</v>
-      </c>
-      <c r="G42" s="3">
-        <v>0</v>
-      </c>
       <c r="H42" s="3">
         <v>0</v>
       </c>
@@ -3395,87 +3575,93 @@
         <v>0</v>
       </c>
       <c r="O42" s="3">
+        <v>0</v>
+      </c>
+      <c r="P42" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="3">
         <v>1199400</v>
       </c>
-      <c r="P42" s="3">
+      <c r="R42" s="3">
         <v>564200</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="S42" s="3">
         <v>867400</v>
       </c>
-      <c r="R42" s="3">
+      <c r="T42" s="3">
         <v>1236100</v>
       </c>
-      <c r="S42" s="3">
+      <c r="U42" s="3">
         <v>603100</v>
       </c>
-      <c r="T42" s="3">
+      <c r="V42" s="3">
         <v>449900</v>
       </c>
-      <c r="U42" s="3">
+      <c r="W42" s="3">
         <v>675000</v>
       </c>
-      <c r="V42" s="3">
+      <c r="X42" s="3">
         <v>613900</v>
       </c>
-      <c r="W42" s="3">
+      <c r="Y42" s="3">
         <v>1119900</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Z42" s="3">
         <v>1208300</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="AA42" s="3">
         <v>536300</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AB42" s="3">
         <v>450400</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AC42" s="3">
         <v>309000</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AD42" s="3">
         <v>439600</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AE42" s="3">
         <v>156500</v>
       </c>
-      <c r="AD42" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AE42" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF42" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG42" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>418600</v>
+      </c>
+      <c r="E43" s="3">
+        <v>411700</v>
+      </c>
+      <c r="F43" s="3">
         <v>741300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>743600</v>
       </c>
-      <c r="F43" s="3">
-        <v>476900</v>
-      </c>
-      <c r="G43" s="3">
-        <v>481500</v>
-      </c>
       <c r="H43" s="3">
+        <v>634200</v>
+      </c>
+      <c r="I43" s="3">
+        <v>640300</v>
+      </c>
+      <c r="J43" s="3">
         <v>897700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>866200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>495300</v>
-      </c>
-      <c r="K43" s="3">
-        <v>496900</v>
-      </c>
-      <c r="L43" s="3">
-        <v>829700</v>
       </c>
       <c r="M43" s="3">
         <v>496900</v>
@@ -3484,87 +3670,93 @@
         <v>829700</v>
       </c>
       <c r="O43" s="3">
+        <v>496900</v>
+      </c>
+      <c r="P43" s="3">
+        <v>829700</v>
+      </c>
+      <c r="Q43" s="3">
         <v>5252700</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>5046700</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>8773400</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>9157800</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>9573500</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>11042000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>5584800</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>5048600</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Y43" s="3">
         <v>5044300</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Z43" s="3">
         <v>5597000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="AA43" s="3">
         <v>5115600</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AB43" s="3">
         <v>4305800</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AC43" s="3">
         <v>4140900</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AD43" s="3">
         <v>2873400</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AE43" s="3">
         <v>2986900</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AF43" s="3">
         <v>2725800</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AG43" s="3">
         <v>2561200</v>
       </c>
     </row>
-    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>2674200</v>
+      </c>
+      <c r="E44" s="3">
+        <v>2630300</v>
+      </c>
+      <c r="F44" s="3">
         <v>2741500</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>2750100</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>2448900</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>2472300</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>2531500</v>
-      </c>
-      <c r="I44" s="3">
-        <v>2442500</v>
-      </c>
-      <c r="J44" s="3">
-        <v>2434800</v>
       </c>
       <c r="K44" s="3">
         <v>2442500</v>
       </c>
       <c r="L44" s="3">
-        <v>2712400</v>
+        <v>2434800</v>
       </c>
       <c r="M44" s="3">
         <v>2442500</v>
@@ -3573,87 +3765,93 @@
         <v>2712400</v>
       </c>
       <c r="O44" s="3">
+        <v>2442500</v>
+      </c>
+      <c r="P44" s="3">
+        <v>2712400</v>
+      </c>
+      <c r="Q44" s="3">
         <v>2481400</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>2358000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="S44" s="3">
         <v>2207100</v>
       </c>
-      <c r="R44" s="3">
+      <c r="T44" s="3">
         <v>2132300</v>
       </c>
-      <c r="S44" s="3">
+      <c r="U44" s="3">
         <v>2084800</v>
       </c>
-      <c r="T44" s="3">
+      <c r="V44" s="3">
         <v>2195000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="W44" s="3">
         <v>2423300</v>
       </c>
-      <c r="V44" s="3">
+      <c r="X44" s="3">
         <v>2281800</v>
       </c>
-      <c r="W44" s="3">
+      <c r="Y44" s="3">
         <v>2292200</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Z44" s="3">
         <v>2468500</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="AA44" s="3">
         <v>2728300</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AB44" s="3">
         <v>2344400</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AC44" s="3">
         <v>2460200</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AD44" s="3">
         <v>1262600</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AE44" s="3">
         <v>1321300</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AF44" s="3">
         <v>1312800</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AG44" s="3">
         <v>1389200</v>
       </c>
     </row>
-    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>13500</v>
+      </c>
+      <c r="E45" s="3">
+        <v>13200</v>
+      </c>
+      <c r="F45" s="3">
         <v>47400</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>47600</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>3198900</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>3229500</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>4112700</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>3968100</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>22700</v>
-      </c>
-      <c r="K45" s="3">
-        <v>22800</v>
-      </c>
-      <c r="L45" s="3">
-        <v>145100</v>
       </c>
       <c r="M45" s="3">
         <v>22800</v>
@@ -3662,87 +3860,93 @@
         <v>145100</v>
       </c>
       <c r="O45" s="3">
+        <v>22800</v>
+      </c>
+      <c r="P45" s="3">
+        <v>145100</v>
+      </c>
+      <c r="Q45" s="3">
         <v>147000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>102400</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>26200</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>6600</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>35700</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>15200</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>50900</v>
       </c>
-      <c r="V45" s="3">
+      <c r="X45" s="3">
         <v>24800</v>
       </c>
-      <c r="W45" s="3">
+      <c r="Y45" s="3">
         <v>57300</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Z45" s="3">
         <v>13600</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="AA45" s="3">
         <v>25500</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AB45" s="3">
         <v>124200</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AC45" s="3">
         <v>175800</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AD45" s="3">
         <v>66500</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AE45" s="3">
         <v>58700</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AF45" s="3">
         <v>90900</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AG45" s="3">
         <v>61900</v>
       </c>
     </row>
-    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>4729300</v>
+      </c>
+      <c r="E46" s="3">
+        <v>4651600</v>
+      </c>
+      <c r="F46" s="3">
         <v>5519500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>5536800</v>
       </c>
-      <c r="F46" s="3">
-        <v>10632500</v>
-      </c>
-      <c r="G46" s="3">
-        <v>10734200</v>
-      </c>
       <c r="H46" s="3">
+        <v>10740700</v>
+      </c>
+      <c r="I46" s="3">
+        <v>10843500</v>
+      </c>
+      <c r="J46" s="3">
         <v>11068500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>10679400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>9578900</v>
-      </c>
-      <c r="K46" s="3">
-        <v>9609000</v>
-      </c>
-      <c r="L46" s="3">
-        <v>10404200</v>
       </c>
       <c r="M46" s="3">
         <v>9609000</v>
@@ -3751,58 +3955,64 @@
         <v>10404200</v>
       </c>
       <c r="O46" s="3">
+        <v>9609000</v>
+      </c>
+      <c r="P46" s="3">
+        <v>10404200</v>
+      </c>
+      <c r="Q46" s="3">
         <v>10639300</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>8846900</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>9399300</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>9378300</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>10098800</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>9608700</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>10106300</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>8930900</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>9609200</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>10715300</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>9948200</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AB46" s="3">
         <v>8336800</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AC46" s="3">
         <v>8469200</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AD46" s="3">
         <v>5755900</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AE46" s="3">
         <v>6018100</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AF46" s="3">
         <v>5821500</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AG46" s="3">
         <v>5878200</v>
       </c>
     </row>
-    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3810,28 +4020,28 @@
         <v>2700</v>
       </c>
       <c r="E47" s="3">
+        <v>2600</v>
+      </c>
+      <c r="F47" s="3">
         <v>2700</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
+        <v>2700</v>
+      </c>
+      <c r="H47" s="3">
         <v>2500</v>
       </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
         <v>2500</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>18400</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>17800</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>24000</v>
-      </c>
-      <c r="K47" s="3">
-        <v>24100</v>
-      </c>
-      <c r="L47" s="3">
-        <v>828500</v>
       </c>
       <c r="M47" s="3">
         <v>24100</v>
@@ -3840,87 +4050,93 @@
         <v>828500</v>
       </c>
       <c r="O47" s="3">
+        <v>24100</v>
+      </c>
+      <c r="P47" s="3">
+        <v>828500</v>
+      </c>
+      <c r="Q47" s="3">
         <v>3070500</v>
       </c>
-      <c r="P47" s="3">
+      <c r="R47" s="3">
         <v>3540300</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="S47" s="3">
         <v>3586200</v>
       </c>
-      <c r="R47" s="3">
+      <c r="T47" s="3">
         <v>7045200</v>
       </c>
-      <c r="S47" s="3">
+      <c r="U47" s="3">
         <v>8344300</v>
       </c>
-      <c r="T47" s="3">
+      <c r="V47" s="3">
         <v>10049700</v>
       </c>
-      <c r="U47" s="3">
+      <c r="W47" s="3">
         <v>5629500</v>
       </c>
-      <c r="V47" s="3">
+      <c r="X47" s="3">
         <v>5034400</v>
       </c>
-      <c r="W47" s="3">
+      <c r="Y47" s="3">
         <v>4342800</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Z47" s="3">
         <v>4293200</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="AA47" s="3">
         <v>4044400</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AB47" s="3">
         <v>3509300</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AC47" s="3">
         <v>3243700</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AD47" s="3">
         <v>3155100</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AE47" s="3">
         <v>2870800</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AF47" s="3">
         <v>2683600</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AG47" s="3">
         <v>2766600</v>
       </c>
     </row>
-    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>18669800</v>
+      </c>
+      <c r="E48" s="3">
+        <v>18362800</v>
+      </c>
+      <c r="F48" s="3">
         <v>18600700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>18659100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>17382700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>17549000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>17832300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>17205400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>17156300</v>
-      </c>
-      <c r="K48" s="3">
-        <v>17210200</v>
-      </c>
-      <c r="L48" s="3">
-        <v>16676000</v>
       </c>
       <c r="M48" s="3">
         <v>17210200</v>
@@ -3929,87 +4145,93 @@
         <v>16676000</v>
       </c>
       <c r="O48" s="3">
+        <v>17210200</v>
+      </c>
+      <c r="P48" s="3">
+        <v>16676000</v>
+      </c>
+      <c r="Q48" s="3">
         <v>18013900</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>18320900</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>17897100</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>28764700</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>28404100</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>28750000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>17149100</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>16780600</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>17492100</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Z48" s="3">
         <v>13498800</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AA48" s="3">
         <v>14078900</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AB48" s="3">
         <v>13215800</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AC48" s="3">
         <v>12974600</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AD48" s="3">
         <v>12735300</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AE48" s="3">
         <v>12722200</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AF48" s="3">
         <v>12704400</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AG48" s="3">
         <v>12620100</v>
       </c>
     </row>
-    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1127800</v>
+      </c>
+      <c r="E49" s="3">
+        <v>1109300</v>
+      </c>
+      <c r="F49" s="3">
         <v>1109900</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>1113300</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>1015600</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>1025300</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>1066000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>1028500</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>1018400</v>
-      </c>
-      <c r="K49" s="3">
-        <v>1021600</v>
-      </c>
-      <c r="L49" s="3">
-        <v>1251400</v>
       </c>
       <c r="M49" s="3">
         <v>1021600</v>
@@ -4018,58 +4240,64 @@
         <v>1251400</v>
       </c>
       <c r="O49" s="3">
+        <v>1021600</v>
+      </c>
+      <c r="P49" s="3">
+        <v>1251400</v>
+      </c>
+      <c r="Q49" s="3">
         <v>1339800</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>1320100</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>1313500</v>
       </c>
-      <c r="R49" s="3">
+      <c r="T49" s="3">
         <v>1199400</v>
       </c>
-      <c r="S49" s="3">
+      <c r="U49" s="3">
         <v>1094000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="V49" s="3">
         <v>1234400</v>
       </c>
-      <c r="U49" s="3">
+      <c r="W49" s="3">
         <v>1250700</v>
       </c>
-      <c r="V49" s="3">
+      <c r="X49" s="3">
         <v>1233800</v>
       </c>
-      <c r="W49" s="3">
+      <c r="Y49" s="3">
         <v>1282100</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Z49" s="3">
         <v>1462000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="AA49" s="3">
         <v>1178800</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AB49" s="3">
         <v>1060600</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AC49" s="3">
         <v>1027800</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AD49" s="3">
         <v>429100</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AE49" s="3">
         <v>448700</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AF49" s="3">
         <v>428000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AG49" s="3">
         <v>399000</v>
       </c>
     </row>
-    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4157,8 +4385,14 @@
       <c r="AE50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4246,37 +4480,43 @@
       <c r="AE51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>790000</v>
+      </c>
+      <c r="E52" s="3">
+        <v>777000</v>
+      </c>
+      <c r="F52" s="3">
         <v>975700</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>978800</v>
       </c>
-      <c r="F52" s="3">
-        <v>1016800</v>
-      </c>
-      <c r="G52" s="3">
-        <v>1026500</v>
-      </c>
       <c r="H52" s="3">
+        <v>1045800</v>
+      </c>
+      <c r="I52" s="3">
+        <v>1055800</v>
+      </c>
+      <c r="J52" s="3">
         <v>1008100</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>972700</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>1094200</v>
-      </c>
-      <c r="K52" s="3">
-        <v>1097700</v>
-      </c>
-      <c r="L52" s="3">
-        <v>1334500</v>
       </c>
       <c r="M52" s="3">
         <v>1097700</v>
@@ -4285,58 +4525,64 @@
         <v>1334500</v>
       </c>
       <c r="O52" s="3">
+        <v>1097700</v>
+      </c>
+      <c r="P52" s="3">
+        <v>1334500</v>
+      </c>
+      <c r="Q52" s="3">
         <v>2489200</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>3285700</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>1495900</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>1018300</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>1298100</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>1430800</v>
       </c>
-      <c r="U52" s="3">
+      <c r="W52" s="3">
         <v>1730900</v>
       </c>
-      <c r="V52" s="3">
+      <c r="X52" s="3">
         <v>1154500</v>
       </c>
-      <c r="W52" s="3">
+      <c r="Y52" s="3">
         <v>356200</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Z52" s="3">
         <v>35500</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="AA52" s="3">
         <v>12700</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AB52" s="3">
         <v>26400</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AC52" s="3">
         <v>60800</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AD52" s="3">
         <v>62600</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AE52" s="3">
         <v>71700</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AF52" s="3">
         <v>138300</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AG52" s="3">
         <v>51400</v>
       </c>
     </row>
-    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4424,37 +4670,43 @@
       <c r="AE53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>25494600</v>
+      </c>
+      <c r="E54" s="3">
+        <v>25075500</v>
+      </c>
+      <c r="F54" s="3">
         <v>26414400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>26497400</v>
       </c>
-      <c r="F54" s="3">
-        <v>31017800</v>
-      </c>
-      <c r="G54" s="3">
-        <v>31314600</v>
-      </c>
       <c r="H54" s="3">
+        <v>31155000</v>
+      </c>
+      <c r="I54" s="3">
+        <v>31453000</v>
+      </c>
+      <c r="J54" s="3">
         <v>32381300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>31242900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>31665500</v>
-      </c>
-      <c r="K54" s="3">
-        <v>31765000</v>
-      </c>
-      <c r="L54" s="3">
-        <v>32455300</v>
       </c>
       <c r="M54" s="3">
         <v>31765000</v>
@@ -4463,58 +4715,64 @@
         <v>32455300</v>
       </c>
       <c r="O54" s="3">
+        <v>31765000</v>
+      </c>
+      <c r="P54" s="3">
+        <v>32455300</v>
+      </c>
+      <c r="Q54" s="3">
         <v>35552700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>35313900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>33692000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>33146200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>34533500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>35404600</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>35866600</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>33134200</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>33082500</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>30004700</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>29263100</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>26149000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>25776000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AD54" s="3">
         <v>22138100</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AE54" s="3">
         <v>22131500</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AF54" s="3">
         <v>21775800</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AG54" s="3">
         <v>21715200</v>
       </c>
     </row>
-    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4546,8 +4804,10 @@
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
-    </row>
-    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF55" s="3"/>
+      <c r="AG55" s="3"/>
+    </row>
+    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4579,37 +4839,39 @@
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
-    </row>
-    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF56" s="3"/>
+      <c r="AG56" s="3"/>
+    </row>
+    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>5154600</v>
+      </c>
+      <c r="E57" s="3">
+        <v>5069900</v>
+      </c>
+      <c r="F57" s="3">
         <v>7561700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>7585400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>4911700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>4958600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>6694200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>6458900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>4755900</v>
-      </c>
-      <c r="K57" s="3">
-        <v>4770900</v>
-      </c>
-      <c r="L57" s="3">
-        <v>6545900</v>
       </c>
       <c r="M57" s="3">
         <v>4770900</v>
@@ -4618,87 +4880,93 @@
         <v>6545900</v>
       </c>
       <c r="O57" s="3">
+        <v>4770900</v>
+      </c>
+      <c r="P57" s="3">
+        <v>6545900</v>
+      </c>
+      <c r="Q57" s="3">
         <v>6516400</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>5965300</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>5987600</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>5889200</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>5995500</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>5417700</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>5844200</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>5172800</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>5833600</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>5894300</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>5920800</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AB57" s="3">
         <v>4941100</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AC57" s="3">
         <v>5511200</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AD57" s="3">
         <v>8151900</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AE57" s="3">
         <v>8526300</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AF57" s="3">
         <v>8369500</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AG57" s="3">
         <v>8190400</v>
       </c>
     </row>
-    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>787300</v>
+      </c>
+      <c r="E58" s="3">
+        <v>774400</v>
+      </c>
+      <c r="F58" s="3">
         <v>798200</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>800700</v>
       </c>
-      <c r="F58" s="3">
-        <v>833100</v>
-      </c>
-      <c r="G58" s="3">
-        <v>841100</v>
-      </c>
       <c r="H58" s="3">
+        <v>698400</v>
+      </c>
+      <c r="I58" s="3">
+        <v>705100</v>
+      </c>
+      <c r="J58" s="3">
         <v>782100</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>754600</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>732900</v>
-      </c>
-      <c r="K58" s="3">
-        <v>735200</v>
-      </c>
-      <c r="L58" s="3">
-        <v>703200</v>
       </c>
       <c r="M58" s="3">
         <v>735200</v>
@@ -4707,87 +4975,93 @@
         <v>703200</v>
       </c>
       <c r="O58" s="3">
+        <v>735200</v>
+      </c>
+      <c r="P58" s="3">
+        <v>703200</v>
+      </c>
+      <c r="Q58" s="3">
         <v>2083800</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>761100</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="S58" s="3">
         <v>1074700</v>
       </c>
-      <c r="R58" s="3">
+      <c r="T58" s="3">
         <v>1154700</v>
       </c>
-      <c r="S58" s="3">
+      <c r="U58" s="3">
         <v>1797900</v>
       </c>
-      <c r="T58" s="3">
+      <c r="V58" s="3">
         <v>707200</v>
       </c>
-      <c r="U58" s="3">
+      <c r="W58" s="3">
         <v>1279300</v>
       </c>
-      <c r="V58" s="3">
+      <c r="X58" s="3">
         <v>1595700</v>
       </c>
-      <c r="W58" s="3">
+      <c r="Y58" s="3">
         <v>933200</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Z58" s="3">
         <v>870100</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="AA58" s="3">
         <v>984900</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AB58" s="3">
         <v>454400</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AC58" s="3">
         <v>586900</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AD58" s="3">
         <v>290900</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AE58" s="3">
         <v>230900</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AF58" s="3">
         <v>342400</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AG58" s="3">
         <v>492500</v>
       </c>
     </row>
-    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1362000</v>
+      </c>
+      <c r="E59" s="3">
+        <v>1339600</v>
+      </c>
+      <c r="F59" s="3">
         <v>323900</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>324900</v>
       </c>
-      <c r="F59" s="3">
-        <v>5337000</v>
-      </c>
-      <c r="G59" s="3">
-        <v>5388100</v>
-      </c>
       <c r="H59" s="3">
+        <v>5282900</v>
+      </c>
+      <c r="I59" s="3">
+        <v>5333400</v>
+      </c>
+      <c r="J59" s="3">
         <v>5273300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>5087900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>1392400</v>
-      </c>
-      <c r="K59" s="3">
-        <v>1396800</v>
-      </c>
-      <c r="L59" s="3">
-        <v>388200</v>
       </c>
       <c r="M59" s="3">
         <v>1396800</v>
@@ -4796,87 +5070,93 @@
         <v>388200</v>
       </c>
       <c r="O59" s="3">
+        <v>1396800</v>
+      </c>
+      <c r="P59" s="3">
+        <v>388200</v>
+      </c>
+      <c r="Q59" s="3">
         <v>6620000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>6222500</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>6957300</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>8478100</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>7789600</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>9146100</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>8557800</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>7247600</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>6802200</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>7285400</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AA59" s="3">
         <v>7275100</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AB59" s="3">
         <v>6172100</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AC59" s="3">
         <v>5257900</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AD59" s="3">
         <v>322200</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AE59" s="3">
         <v>277800</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AF59" s="3">
         <v>404300</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AG59" s="3">
         <v>358200</v>
       </c>
     </row>
-    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>8520600</v>
+      </c>
+      <c r="E60" s="3">
+        <v>8380500</v>
+      </c>
+      <c r="F60" s="3">
         <v>8870800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>8898600</v>
       </c>
-      <c r="F60" s="3">
-        <v>14367500</v>
-      </c>
-      <c r="G60" s="3">
-        <v>14505000</v>
-      </c>
       <c r="H60" s="3">
+        <v>14326000</v>
+      </c>
+      <c r="I60" s="3">
+        <v>14463000</v>
+      </c>
+      <c r="J60" s="3">
         <v>14877600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>14354600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>14470000</v>
-      </c>
-      <c r="K60" s="3">
-        <v>14515500</v>
-      </c>
-      <c r="L60" s="3">
-        <v>14379100</v>
       </c>
       <c r="M60" s="3">
         <v>14515500</v>
@@ -4885,87 +5165,93 @@
         <v>14379100</v>
       </c>
       <c r="O60" s="3">
+        <v>14515500</v>
+      </c>
+      <c r="P60" s="3">
+        <v>14379100</v>
+      </c>
+      <c r="Q60" s="3">
         <v>15220200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>12948800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>14019500</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>15522000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>15583000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>15271000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>15681200</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>14016200</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>13568900</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>14049800</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>14180800</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AB60" s="3">
         <v>11340300</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AC60" s="3">
         <v>11062600</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AD60" s="3">
         <v>8765000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AE60" s="3">
         <v>9035000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AF60" s="3">
         <v>9116100</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AG60" s="3">
         <v>9041100</v>
       </c>
     </row>
-    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>8096700</v>
+      </c>
+      <c r="E61" s="3">
+        <v>7963600</v>
+      </c>
+      <c r="F61" s="3">
         <v>8061700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>8087100</v>
       </c>
-      <c r="F61" s="3">
-        <v>7482600</v>
-      </c>
-      <c r="G61" s="3">
-        <v>7554200</v>
-      </c>
       <c r="H61" s="3">
+        <v>7617300</v>
+      </c>
+      <c r="I61" s="3">
+        <v>7690200</v>
+      </c>
+      <c r="J61" s="3">
         <v>7908700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>7630700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>7542000</v>
-      </c>
-      <c r="K61" s="3">
-        <v>7565800</v>
-      </c>
-      <c r="L61" s="3">
-        <v>7639700</v>
       </c>
       <c r="M61" s="3">
         <v>7565800</v>
@@ -4974,147 +5260,159 @@
         <v>7639700</v>
       </c>
       <c r="O61" s="3">
+        <v>7565800</v>
+      </c>
+      <c r="P61" s="3">
+        <v>7639700</v>
+      </c>
+      <c r="Q61" s="3">
         <v>7452000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>8925600</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>8510900</v>
       </c>
-      <c r="R61" s="3">
+      <c r="T61" s="3">
         <v>7949300</v>
       </c>
-      <c r="S61" s="3">
+      <c r="U61" s="3">
         <v>7830400</v>
       </c>
-      <c r="T61" s="3">
+      <c r="V61" s="3">
         <v>8252700</v>
       </c>
-      <c r="U61" s="3">
+      <c r="W61" s="3">
         <v>7771100</v>
       </c>
-      <c r="V61" s="3">
+      <c r="X61" s="3">
         <v>7265400</v>
       </c>
-      <c r="W61" s="3">
+      <c r="Y61" s="3">
         <v>8113600</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Z61" s="3">
         <v>2184800</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="AA61" s="3">
         <v>2042000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AB61" s="3">
         <v>2693100</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AC61" s="3">
         <v>2731700</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AD61" s="3">
         <v>2856400</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AE61" s="3">
         <v>3018200</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AF61" s="3">
         <v>3299900</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AG61" s="3">
         <v>3443400</v>
       </c>
     </row>
-    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>162800</v>
+      </c>
+      <c r="E62" s="3">
+        <v>160200</v>
+      </c>
+      <c r="F62" s="3">
         <v>207300</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>208000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>241600</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>243900</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>395600</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>381700</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>299500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>300400</v>
-      </c>
-      <c r="L62" s="3">
-        <v>182300</v>
-      </c>
-      <c r="M62" s="3">
-        <v>299100</v>
       </c>
       <c r="N62" s="3">
         <v>182300</v>
       </c>
       <c r="O62" s="3">
+        <v>299100</v>
+      </c>
+      <c r="P62" s="3">
+        <v>182300</v>
+      </c>
+      <c r="Q62" s="3">
         <v>2476100</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>2386900</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>1763600</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>881800</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>1956000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>2007400</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>2604400</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>2647300</v>
       </c>
-      <c r="W62" s="3">
+      <c r="Y62" s="3">
         <v>2648400</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Z62" s="3">
         <v>3663100</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="AA62" s="3">
         <v>3223600</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AB62" s="3">
         <v>3039100</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AC62" s="3">
         <v>3586300</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AD62" s="3">
         <v>2214700</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AE62" s="3">
         <v>1977300</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AF62" s="3">
         <v>2066000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AG62" s="3">
         <v>1966000</v>
       </c>
     </row>
-    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5202,8 +5500,14 @@
       <c r="AE63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5291,8 +5595,14 @@
       <c r="AE64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5380,37 +5690,43 @@
       <c r="AE65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>17217600</v>
+      </c>
+      <c r="E66" s="3">
+        <v>16934500</v>
+      </c>
+      <c r="F66" s="3">
         <v>17751000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>17806700</v>
       </c>
-      <c r="F66" s="3">
-        <v>22648000</v>
-      </c>
-      <c r="G66" s="3">
-        <v>22864700</v>
-      </c>
       <c r="H66" s="3">
+        <v>22641700</v>
+      </c>
+      <c r="I66" s="3">
+        <v>22858300</v>
+      </c>
+      <c r="J66" s="3">
         <v>23689200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>22856500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>22987500</v>
-      </c>
-      <c r="K66" s="3">
-        <v>23059800</v>
-      </c>
-      <c r="L66" s="3">
-        <v>23497200</v>
       </c>
       <c r="M66" s="3">
         <v>23059800</v>
@@ -5419,58 +5735,64 @@
         <v>23497200</v>
       </c>
       <c r="O66" s="3">
+        <v>23059800</v>
+      </c>
+      <c r="P66" s="3">
+        <v>23497200</v>
+      </c>
+      <c r="Q66" s="3">
         <v>25148300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>24261300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>24294100</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>24353100</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>25369400</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>25531000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>26056800</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>23928900</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>24330900</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>19897700</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>19446400</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>17072500</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>17380500</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AD66" s="3">
         <v>13836100</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AE66" s="3">
         <v>14030500</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AF66" s="3">
         <v>14482100</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AG66" s="3">
         <v>14450500</v>
       </c>
     </row>
-    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5502,8 +5824,10 @@
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
-    </row>
-    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF67" s="3"/>
+      <c r="AG67" s="3"/>
+    </row>
+    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5591,8 +5915,14 @@
       <c r="AE68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5680,8 +6010,14 @@
       <c r="AE69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5769,8 +6105,14 @@
       <c r="AE70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5858,37 +6200,43 @@
       <c r="AE71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>5289200</v>
+      </c>
+      <c r="E72" s="3">
+        <v>5202300</v>
+      </c>
+      <c r="F72" s="3">
         <v>5576400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>5593900</v>
       </c>
-      <c r="F72" s="3">
-        <v>5556000</v>
-      </c>
-      <c r="G72" s="3">
-        <v>5609100</v>
-      </c>
       <c r="H72" s="3">
+        <v>5699400</v>
+      </c>
+      <c r="I72" s="3">
+        <v>5754000</v>
+      </c>
+      <c r="J72" s="3">
         <v>5268100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>5082900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>4090100</v>
-      </c>
-      <c r="K72" s="3">
-        <v>4102900</v>
-      </c>
-      <c r="L72" s="3">
-        <v>4407700</v>
       </c>
       <c r="M72" s="3">
         <v>4102900</v>
@@ -5897,58 +6245,64 @@
         <v>4407700</v>
       </c>
       <c r="O72" s="3">
+        <v>4102900</v>
+      </c>
+      <c r="P72" s="3">
+        <v>4407700</v>
+      </c>
+      <c r="Q72" s="3">
         <v>7677700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>8331200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>6689600</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>6092500</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>6555300</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>6972700</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>6982000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>6516600</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>5988500</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>7034400</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>6639700</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>6116600</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>5500900</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AD72" s="3">
         <v>5484600</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AE72" s="3">
         <v>5285100</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AF72" s="3">
         <v>5113100</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AG72" s="3">
         <v>5098600</v>
       </c>
     </row>
-    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6036,8 +6390,14 @@
       <c r="AE73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6125,8 +6485,14 @@
       <c r="AE74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6214,37 +6580,43 @@
       <c r="AE75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>8277000</v>
+      </c>
+      <c r="E76" s="3">
+        <v>8141000</v>
+      </c>
+      <c r="F76" s="3">
         <v>8663400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>8690600</v>
       </c>
-      <c r="F76" s="3">
-        <v>8369800</v>
-      </c>
-      <c r="G76" s="3">
-        <v>8449900</v>
-      </c>
       <c r="H76" s="3">
+        <v>8513300</v>
+      </c>
+      <c r="I76" s="3">
+        <v>8594700</v>
+      </c>
+      <c r="J76" s="3">
         <v>8692100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>8386500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>8678000</v>
-      </c>
-      <c r="K76" s="3">
-        <v>8705200</v>
-      </c>
-      <c r="L76" s="3">
-        <v>8958100</v>
       </c>
       <c r="M76" s="3">
         <v>8705200</v>
@@ -6253,58 +6625,64 @@
         <v>8958100</v>
       </c>
       <c r="O76" s="3">
+        <v>8705200</v>
+      </c>
+      <c r="P76" s="3">
+        <v>8958100</v>
+      </c>
+      <c r="Q76" s="3">
         <v>10404400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>11052700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>9398000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>8793100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>9164100</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>9873500</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>9809800</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>9205300</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>8751600</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>10107000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>9816600</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>9076500</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>8395500</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>8301900</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AE76" s="3">
         <v>8101100</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AF76" s="3">
         <v>7293700</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AG76" s="3">
         <v>7264700</v>
       </c>
     </row>
-    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6392,42 +6770,48 @@
       <c r="AE77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46081</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45991</v>
+      </c>
+      <c r="F80" s="2">
         <v>45913</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45821</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45717</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45627</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45549</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45457</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45353</v>
-      </c>
-      <c r="K80" s="2">
-        <v>45262</v>
-      </c>
-      <c r="L80" s="2">
-        <v>45185</v>
       </c>
       <c r="M80" s="2">
         <v>45262</v>
@@ -6436,58 +6820,64 @@
         <v>45185</v>
       </c>
       <c r="O80" s="2">
+        <v>45262</v>
+      </c>
+      <c r="P80" s="2">
+        <v>45185</v>
+      </c>
+      <c r="Q80" s="2">
         <v>44821</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44625</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44457</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44261</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>44093</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43897</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43729</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43533</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43365</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>43169</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43001</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>42805</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>42637</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>42441</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>42273</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>42077</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>41909</v>
       </c>
     </row>
-    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -6524,59 +6914,65 @@
       <c r="N81" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O81" s="3">
+      <c r="O81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q81" s="3">
         <v>374000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>377900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>496000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>-31500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>-233300</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>225600</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>-60800</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>65100</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>137800</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>184100</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>220800</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>92500</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>373600</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>256900</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3">
         <v>341700</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AF81" s="3">
         <v>234400</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AG81" s="3">
         <v>-453000</v>
       </c>
     </row>
-    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6608,37 +7004,39 @@
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
-    </row>
-    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF82" s="3"/>
+      <c r="AG82" s="3"/>
+    </row>
+    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>241600</v>
+      </c>
+      <c r="E83" s="3">
+        <v>243900</v>
+      </c>
+      <c r="F83" s="3">
         <v>349600</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>337300</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>282400</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>283300</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>323700</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>334600</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>239600</v>
-      </c>
-      <c r="K83" s="3">
-        <v>245000</v>
-      </c>
-      <c r="L83" s="3">
-        <v>315200</v>
       </c>
       <c r="M83" s="3">
         <v>245000</v>
@@ -6647,58 +7045,64 @@
         <v>315200</v>
       </c>
       <c r="O83" s="3">
+        <v>245000</v>
+      </c>
+      <c r="P83" s="3">
+        <v>315200</v>
+      </c>
+      <c r="Q83" s="3">
         <v>852900</v>
       </c>
-      <c r="P83" s="3">
+      <c r="R83" s="3">
         <v>736100</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="S83" s="3">
         <v>864700</v>
       </c>
-      <c r="R83" s="3">
+      <c r="T83" s="3">
         <v>771600</v>
       </c>
-      <c r="S83" s="3">
+      <c r="U83" s="3">
         <v>842800</v>
       </c>
-      <c r="T83" s="3">
+      <c r="V83" s="3">
         <v>746400</v>
       </c>
-      <c r="U83" s="3">
+      <c r="W83" s="3">
         <v>827600</v>
       </c>
-      <c r="V83" s="3">
+      <c r="X83" s="3">
         <v>687300</v>
       </c>
-      <c r="W83" s="3">
+      <c r="Y83" s="3">
         <v>830800</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Z83" s="3">
         <v>503200</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="AA83" s="3">
         <v>512300</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AB83" s="3">
         <v>397600</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AC83" s="3">
         <v>422700</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AD83" s="3">
         <v>360000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AE83" s="3">
         <v>401700</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AF83" s="3">
         <v>343700</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AG83" s="3">
         <v>418700</v>
       </c>
     </row>
-    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6786,8 +7190,14 @@
       <c r="AE84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6875,8 +7285,14 @@
       <c r="AE85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6964,8 +7380,14 @@
       <c r="AE86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7053,8 +7475,14 @@
       <c r="AE87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7142,97 +7570,109 @@
       <c r="AE88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>778600</v>
+      </c>
+      <c r="E89" s="3">
+        <v>765800</v>
+      </c>
+      <c r="F89" s="3">
         <v>-68400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-68600</v>
       </c>
-      <c r="F89" s="3">
-        <v>822400</v>
-      </c>
-      <c r="G89" s="3">
-        <v>830300</v>
-      </c>
       <c r="H89" s="3">
+        <v>950700</v>
+      </c>
+      <c r="I89" s="3">
+        <v>959800</v>
+      </c>
+      <c r="J89" s="3">
         <v>418000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>403300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>156000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>156500</v>
-      </c>
-      <c r="L89" s="3">
-        <v>1065300</v>
-      </c>
-      <c r="M89" s="3">
-        <v>431600</v>
       </c>
       <c r="N89" s="3">
         <v>1065300</v>
       </c>
       <c r="O89" s="3">
+        <v>431600</v>
+      </c>
+      <c r="P89" s="3">
+        <v>1065300</v>
+      </c>
+      <c r="Q89" s="3">
         <v>2057500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>126000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>1198000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>1091800</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>1926700</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>441000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>1270600</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>105300</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>1163800</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>782800</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>1119400</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>537600</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>964400</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AD89" s="3">
         <v>189100</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AE89" s="3">
         <v>322200</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AF89" s="3">
         <v>675500</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AG89" s="3">
         <v>524100</v>
       </c>
     </row>
-    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7264,37 +7704,39 @@
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
-    </row>
-    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF90" s="3"/>
+      <c r="AG90" s="3"/>
+    </row>
+    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-169600</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-166800</v>
+      </c>
+      <c r="F91" s="3">
         <v>-244600</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-245400</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-202000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-203900</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-194500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-187700</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-214800</v>
-      </c>
-      <c r="K91" s="3">
-        <v>-215500</v>
-      </c>
-      <c r="L91" s="3">
-        <v>-645500</v>
       </c>
       <c r="M91" s="3">
         <v>-215500</v>
@@ -7303,58 +7745,64 @@
         <v>-645500</v>
       </c>
       <c r="O91" s="3">
+        <v>-215500</v>
+      </c>
+      <c r="P91" s="3">
+        <v>-645500</v>
+      </c>
+      <c r="Q91" s="3">
         <v>-308000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-375000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="S91" s="3">
         <v>-319000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="T91" s="3">
         <v>-294000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="U91" s="3">
         <v>-301000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="V91" s="3">
         <v>-374000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="W91" s="3">
         <v>-265000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="X91" s="3">
         <v>-282700</v>
       </c>
-      <c r="W91" s="3">
+      <c r="Y91" s="3">
         <v>-286700</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Z91" s="3">
         <v>-380500</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="AA91" s="3">
         <v>-399100</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AB91" s="3">
         <v>-431900</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AC91" s="3">
         <v>-396900</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AD91" s="3">
         <v>-373000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AE91" s="3">
         <v>-469600</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AF91" s="3">
         <v>-583300</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AG91" s="3">
         <v>-771600</v>
       </c>
     </row>
-    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7442,8 +7890,14 @@
       <c r="AE92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7531,97 +7985,109 @@
       <c r="AE93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-33600</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-33100</v>
+      </c>
+      <c r="F94" s="3">
         <v>-499400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-500900</v>
       </c>
-      <c r="F94" s="3">
-        <v>232200</v>
-      </c>
-      <c r="G94" s="3">
-        <v>234400</v>
-      </c>
       <c r="H94" s="3">
+        <v>-239700</v>
+      </c>
+      <c r="I94" s="3">
+        <v>-242000</v>
+      </c>
+      <c r="J94" s="3">
         <v>-266800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-257400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>23400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>23400</v>
-      </c>
-      <c r="L94" s="3">
-        <v>-652400</v>
-      </c>
-      <c r="M94" s="3">
-        <v>-251600</v>
       </c>
       <c r="N94" s="3">
         <v>-652400</v>
       </c>
       <c r="O94" s="3">
+        <v>-251600</v>
+      </c>
+      <c r="P94" s="3">
+        <v>-652400</v>
+      </c>
+      <c r="Q94" s="3">
         <v>-379200</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-482900</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-368700</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>-380500</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>-335400</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>-422000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>-115400</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>-308700</v>
       </c>
-      <c r="W94" s="3">
+      <c r="Y94" s="3">
         <v>-259800</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Z94" s="3">
         <v>-261800</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="AA94" s="3">
         <v>-393400</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AB94" s="3">
         <v>-394900</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AC94" s="3">
         <v>-583100</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AD94" s="3">
         <v>-113500</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AE94" s="3">
         <v>-408200</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AF94" s="3">
         <v>-454300</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AG94" s="3">
         <v>-730800</v>
       </c>
     </row>
-    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7653,37 +8119,39 @@
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
-    </row>
-    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF95" s="3"/>
+      <c r="AG95" s="3"/>
+    </row>
+    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>62600</v>
+      </c>
+      <c r="E96" s="3">
+        <v>61600</v>
+      </c>
+      <c r="F96" s="3">
         <v>151100</v>
       </c>
-      <c r="E96" s="3">
+      <c r="G96" s="3">
         <v>151600</v>
       </c>
-      <c r="F96" s="3">
+      <c r="H96" s="3">
         <v>57300</v>
       </c>
-      <c r="G96" s="3">
+      <c r="I96" s="3">
         <v>57800</v>
       </c>
-      <c r="H96" s="3">
+      <c r="J96" s="3">
         <v>142600</v>
       </c>
-      <c r="I96" s="3">
+      <c r="K96" s="3">
         <v>137600</v>
       </c>
-      <c r="J96" s="3">
+      <c r="L96" s="3">
         <v>57500</v>
-      </c>
-      <c r="K96" s="3">
-        <v>57700</v>
-      </c>
-      <c r="L96" s="3">
-        <v>133300</v>
       </c>
       <c r="M96" s="3">
         <v>57700</v>
@@ -7692,58 +8160,64 @@
         <v>133300</v>
       </c>
       <c r="O96" s="3">
-        <v>0</v>
+        <v>57700</v>
       </c>
       <c r="P96" s="3">
-        <v>0</v>
+        <v>133300</v>
       </c>
       <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+      <c r="R96" s="3">
+        <v>0</v>
+      </c>
+      <c r="S96" s="3">
         <v>-5200</v>
       </c>
-      <c r="R96" s="3">
+      <c r="T96" s="3">
         <v>-30200</v>
       </c>
-      <c r="S96" s="3">
-        <v>0</v>
-      </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
+        <v>0</v>
+      </c>
+      <c r="V96" s="3">
         <v>-3800</v>
       </c>
-      <c r="U96" s="3">
+      <c r="W96" s="3">
         <v>-24800</v>
       </c>
-      <c r="V96" s="3">
+      <c r="X96" s="3">
         <v>-3500</v>
       </c>
-      <c r="W96" s="3">
+      <c r="Y96" s="3">
         <v>-24400</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Z96" s="3">
         <v>-4100</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="AA96" s="3">
         <v>-28300</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AB96" s="3">
         <v>-4000</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AC96" s="3">
         <v>-25900</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AD96" s="3">
         <v>199600</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AE96" s="3">
         <v>-204800</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AF96" s="3">
         <v>-126400</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AG96" s="3">
         <v>-308100</v>
       </c>
     </row>
-    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7831,8 +8305,14 @@
       <c r="AE97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7920,8 +8400,14 @@
       <c r="AE98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8009,37 +8495,43 @@
       <c r="AE99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-522200</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-513600</v>
+      </c>
+      <c r="F100" s="3">
         <v>-439100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-440400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-306400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>-309400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>-414000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-399500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-228700</v>
-      </c>
-      <c r="K100" s="3">
-        <v>-229400</v>
-      </c>
-      <c r="L100" s="3">
-        <v>49600</v>
       </c>
       <c r="M100" s="3">
         <v>-229400</v>
@@ -8048,58 +8540,64 @@
         <v>49600</v>
       </c>
       <c r="O100" s="3">
+        <v>-229400</v>
+      </c>
+      <c r="P100" s="3">
+        <v>49600</v>
+      </c>
+      <c r="Q100" s="3">
         <v>-682300</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>-452700</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>-883100</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>-681000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>-1006100</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>-618400</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>-724600</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>-4700</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>-912500</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Z100" s="3">
         <v>19100</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="AA100" s="3">
         <v>-365100</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AB100" s="3">
         <v>-281300</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AC100" s="3">
         <v>-327100</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AD100" s="3">
         <v>-233500</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AE100" s="3">
         <v>66500</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AF100" s="3">
         <v>-385800</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AG100" s="3">
         <v>-27700</v>
       </c>
     </row>
-    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8136,11 +8634,11 @@
       <c r="N101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
-      </c>
-      <c r="P101" s="3">
-        <v>0</v>
+      <c r="O101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q101" s="3">
         <v>0</v>
@@ -8187,37 +8685,43 @@
       <c r="AE101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>222700</v>
+      </c>
+      <c r="E102" s="3">
+        <v>219100</v>
+      </c>
+      <c r="F102" s="3">
         <v>-1006900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-1010000</v>
       </c>
-      <c r="F102" s="3">
-        <v>748100</v>
-      </c>
-      <c r="G102" s="3">
-        <v>755300</v>
-      </c>
       <c r="H102" s="3">
+        <v>404600</v>
+      </c>
+      <c r="I102" s="3">
+        <v>408500</v>
+      </c>
+      <c r="J102" s="3">
         <v>-262900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-253600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-49300</v>
-      </c>
-      <c r="K102" s="3">
-        <v>-49400</v>
-      </c>
-      <c r="L102" s="3">
-        <v>462600</v>
       </c>
       <c r="M102" s="3">
         <v>-49400</v>
@@ -8226,54 +8730,60 @@
         <v>462600</v>
       </c>
       <c r="O102" s="3">
+        <v>-49400</v>
+      </c>
+      <c r="P102" s="3">
+        <v>462600</v>
+      </c>
+      <c r="Q102" s="3">
         <v>996000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>-809600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>-53800</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>30200</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>585300</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>-599400</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>430600</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>-404600</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>-324500</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>540100</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>360900</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>-138700</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>54300</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AD102" s="3">
         <v>-157800</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AE102" s="3">
         <v>-19600</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AF102" s="3">
         <v>-164600</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AG102" s="3">
         <v>-234400</v>
       </c>
     </row>
